--- a/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
+++ b/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
@@ -139,6 +139,19 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFA6A6A6"/>
@@ -157,24 +170,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA6A6A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA6A6A6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -243,8 +243,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -606,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -698,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="130" customHeight="1" s="24">
+    <row r="2" ht="130" customHeight="1" s="24">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>D-01</t>
@@ -769,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="3" hidden="1" ht="130" customHeight="1" s="24">
+    <row r="3" ht="130" customHeight="1" s="24">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>D-02</t>
@@ -854,35 +853,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>權限可視化雙模式</t>
+          <t>員工列表的權限可視化雙模式</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>提供樹狀圖形化與列表模式，方便勾選與檢視各角色的權限範圍。</t>
+          <t>提供樹狀圖形化與列表模式，方便勾選與檢視各員工的權限範圍。</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>RBAC 設定 UI 需支援雙模式切換：(A) 樹狀圖 + 勾選框（直觀）、(B) 列表 + 下拉（細節）。目前僅 (B)。</t>
+          <t>【討論後修正】客戶實際需求是「員工權限可視化全覽」（員工×角色矩陣），不是角色管理頁的雙模式 UI。即：在 /settings/users 提供矩陣視圖，使 HR / 主管能一次看到全公司所有員工的角色與指派層級分布，不必逐個點員工開 modal 才能查詢。</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>部分實作。
-• 已具：列表模式 + 模組分組展開摺疊 + 下拉選單(src/app/features/tenant-admin/pages/role-management-page/role-management-page.component.html:92-150)；permission-visualization-page 提供組織樹+使用者權限查詢。
-• 缺：樹狀圖 + 勾選框形式的權限矩陣，與雙模式切換按鈕。</t>
+          <t>完全實作。
+• 在 /settings/users 加「員工×角色矩陣」第三種視圖（既有 list/card 視圖共用同一頁）
+• 元件：features/organization/components/employee-role-matrix（CDK Virtual Scroll，500 員工流暢）
+• Cell 顯示「● 全集團 / 子公司 / 部門」三類，取最廣 scope；tooltip 列所有指派細節
+• 點員工列 → 開既有 AccountPermissionComponent modal（複用零修改）
+• 角色欄頭點擊 → role-holders-popover 反向查詢持有者
+• 篩選列：搜尋 / 部門 / 角色多選 / 員工狀態，含 URL query params 同步
+• 員工視角 CSV 匯出（中文化、UTF-8 BOM）
+• 順手清理 2 個孤兒元件（permission-visualization-page、user-management-page）</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>前端：role-management-page 加 viewMode signal('tree' | 'list') 與切換按鈕
-新元件：permission-tree-matrix（複用現有 org-tree 元件邏輯但以 feature 階層為骨架）</t>
+          <t>前端新增：employee-role-matrix、role-holders-popover 兩個 standalone 元件 + role-matrix-csv 工具
+前端修改：employee-management-page（加矩陣視圖整合）、view-toggle 共用元件（擴 3 模式 + Signal API）、tenant-admin model（TenantUser interface 對齊）、tenant-admin.service（getUsers 加 ?all=true 選項）、account-permission modal（允許同角色多 scope 指派 + 修正名詞）
+後端修改：tenant-admin.js GET /users 加 ?all=true 分支 + SELECT 補 employee_no / org_unit_id
+相依：新增 @angular/cdk@^18.2 套件
+刪除：tenant-admin/pages/permission-visualization-page、user-management-page（兩個未掛路由的孤兒）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -893,8 +901,11 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1) 樹狀模式的層級切點是「模組 → 功能 → 動作」三層嗎？還是要含 row-level？
-2) 勾選父節點時，是否級聯勾選/取消子節點？</t>
+          <t>【已收斂】
+1. 樹狀勾選方案不採納；改為員工×角色矩陣（鳥瞰視角更符合需求）
+2. 多 scope 指派以「最廣 scope」單一 chip 呈現（呼應後端 perm 取 max 邏輯），細節入 tooltip
+3. global / group 視覺合併為「全集團」，避免與功能權限的編輯範圍 (perm_scope=company) 「全公司」名詞衝突
+4. 矩陣 cell 不顯示 row-level 權限（屬 D-02 範疇）</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
@@ -904,11 +915,28 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>尚未修正</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>OpenSpec change：employee-role-matrix-view（spec-driven schema）。
+主要決議：
+• Cell 採「●符號 + 完整中文分類標籤」單 chip，取最廣 scope
+• 三類分類：全集團 / 子公司 / 部門（global+group 合併）
+• 共用 view-toggle 三模式擴充，4 個既有頁向下相容
+• 篩選列同步 URL query params；矩陣 modal 關閉時失效 cache 並重抓</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>D-03 已完工封存於 2026-05-08。
+• 變更目錄：openspec/changes/archive/2026-05-08-employee-role-matrix-view/
+• 主 spec 同步：openspec/specs/user-overview-lite/spec.md（added 4 / modified 2 / removed 2 requirements）
+• 65/66 tasks 完成（剩 1 個是 archive 動作本身）；含完成驗證跑 tsc + ng build 通過
+• 已知限制：scope 為 metadata-only（middleware 不檢查 user_roles.org_unit_id），屬 D-02 row-level 範疇</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="130" customHeight="1" s="24">
       <c r="A5" s="2" t="inlineStr">
@@ -938,14 +966,19 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未實作。
-• 系統僅有 server/src/routes/export.js（月度檢核報表 Excel 匯出），無權限表匯出。
-• TenantAdminService 未提供 exportRolePermissions() 等 API。</t>
+          <t>完全實作（scope 經客戶確認後縮減為員工視角 CSV，HTML 與角色視角 CSV 不做）。
+• 員工視角 CSV 匯出（features/organization/utils/role-matrix-csv.ts）
+  - 9 欄：員工編號 / 姓名 / Email / 部門 / 角色 / scope_type / scope_name / 帳號狀態 / 匯出時間
+  - 中文化值：全集團 / 子公司 / 部門 / 啟用 / 停用 / 鎖定
+  - UTF-8 BOM、CRLF、escape 處理、檔名 員工權限總覽_&lt;YYYYMMDD-HHmm&gt;.csv
+  - 8 個單元測試覆蓋多角色 / 無角色 / 多 scope / 中文 / escape
+• 入口：/settings/users 矩陣視圖右上「匯出 CSV」按鈕，匯出範圍 = 當前篩選結果
+• 內控留存可用：員工視角已涵蓋「誰持有什麼角色於哪個 scope」的稽核需求</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -963,9 +996,11 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1) 匯出格式：CSV 是純表格？HTML 是否要含公司 logo/簽核欄位？
-2) 是匯出單一角色 還是整租戶所有角色合併一份？
-3) 是否需要 PDF 格式？（從 HTML 印出即可，但要不要做按鈕）</t>
+          <t>【已收斂】
+1. CSV 格式：純表格 ✓ 已實作
+2. HTML 格式：客戶決定不做（避免列印分頁 / 簽核欄位等過度設計）
+3. 角色視角 CSV（角色×功能對照表）：客戶決定不做（員工視角已能滿足內控留存需求）
+4. PDF：以 Excel 開啟 CSV 後直接另存 PDF 替代</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -975,13 +1010,24 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>尚未修正</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="130" customHeight="1" s="24">
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>員工視角 CSV 隨 D-03 同 change 完成（employee-role-matrix-view）。
+HTML 與角色視角 CSV 經客戶確認不納入本次 scope，視為 D-04 完工。</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>D-04 視為完工於 2026-05-08（同 D-03 archive 日期）。
+Scope 縮減決議：客戶確認以 CSV 員工視角作為內控留存格式即可，不另做 HTML 列印模板。
+相關檔案：openspec/changes/archive/2026-05-08-employee-role-matrix-view/specs/user-overview-lite/spec.md（Employee-perspective CSV export requirement）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1" s="24">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>D-05</t>
@@ -1052,7 +1098,7 @@
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
     </row>
-    <row r="7" hidden="1" ht="130" customHeight="1" s="24">
+    <row r="7" ht="130" customHeight="1" s="24">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>D-06</t>
@@ -1197,7 +1243,7 @@
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
     </row>
-    <row r="9" hidden="1" ht="130" customHeight="1" s="24">
+    <row r="9" ht="130" customHeight="1" s="24">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>D-08</t>
@@ -1989,14 +2035,7 @@
       <c r="N18" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18">
-    <filterColumn colId="10" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="中"/>
-        <filter val="低"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2091,7 +2130,7 @@
           <t>純設定/小幅 UI 調整、無 schema 變動</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n"/>
+      <c r="C6" s="26" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
@@ -2104,7 +2143,7 @@
           <t>新增 schema 欄位 + API + 1-2 元件，影響範圍可控</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
+      <c r="C7" s="26" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="24">
       <c r="A8" s="7" t="inlineStr">
@@ -2117,7 +2156,7 @@
           <t>跨層大改 / 新模組 / 破壞既有資料模型 / 多遷移同步</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n"/>
+      <c r="C8" s="26" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1" s="24">
       <c r="A9" s="4" t="inlineStr">
@@ -2130,7 +2169,7 @@
           <t>已實作項目（無需修改）</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n"/>
+      <c r="C9" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -2259,7 +2298,7 @@
           <t>L0_權限與系統設定_需求確認單_1150424.pdf</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n"/>
+      <c r="C20" s="26" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1" s="24">
       <c r="A21" s="12" t="inlineStr">
@@ -2272,7 +2311,7 @@
           <t>PDF（Claude Code Read 工具原生解析）</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n"/>
+      <c r="C21" s="26" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1" s="24">
       <c r="A22" s="12" t="inlineStr">
@@ -2285,7 +2324,7 @@
           <t>4 頁</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n"/>
+      <c r="C22" s="26" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1" s="24">
       <c r="A23" s="12" t="inlineStr">
@@ -2298,7 +2337,7 @@
           <t>SaaS 模組需求確認單 (PRD)</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n"/>
+      <c r="C23" s="26" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1" s="24">
       <c r="A24" s="12" t="inlineStr">
@@ -2311,7 +2350,7 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n"/>
+      <c r="C24" s="26" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1" s="24">
       <c r="A25" s="12" t="inlineStr">
@@ -2324,13 +2363,13 @@
           <t>Bombus 多租戶 SaaS（租戶管理模組為主）</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n"/>
+      <c r="C25" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B7:C7"/>
@@ -2413,13 +2452,13 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="17" t="n">
         <v>5</v>
@@ -2553,13 +2592,13 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="22" t="n">
         <v>17</v>

--- a/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
+++ b/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
@@ -238,12 +238,12 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -612,20 +612,20 @@
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="8" customWidth="1" style="24" min="1" max="1"/>
-    <col width="14" customWidth="1" style="24" min="2" max="2"/>
-    <col width="18" customWidth="1" style="24" min="3" max="3"/>
-    <col width="50" customWidth="1" style="24" min="4" max="5"/>
-    <col width="10" customWidth="1" style="24" min="6" max="6"/>
-    <col width="60" customWidth="1" style="24" min="7" max="7"/>
-    <col width="42" customWidth="1" style="24" min="8" max="10"/>
-    <col width="12" customWidth="1" style="24" min="11" max="11"/>
-    <col width="14" customWidth="1" style="24" min="12" max="12"/>
-    <col width="50" customWidth="1" style="24" min="13" max="13"/>
-    <col width="40" customWidth="1" style="24" min="14" max="14"/>
+    <col width="8" customWidth="1" style="26" min="1" max="1"/>
+    <col width="14" customWidth="1" style="26" min="2" max="2"/>
+    <col width="18" customWidth="1" style="26" min="3" max="3"/>
+    <col width="50" customWidth="1" style="26" min="4" max="5"/>
+    <col width="10" customWidth="1" style="26" min="6" max="6"/>
+    <col width="60" customWidth="1" style="26" min="7" max="7"/>
+    <col width="42" customWidth="1" style="26" min="8" max="10"/>
+    <col width="12" customWidth="1" style="26" min="11" max="11"/>
+    <col width="14" customWidth="1" style="26" min="12" max="12"/>
+    <col width="50" customWidth="1" style="26" min="13" max="13"/>
+    <col width="40" customWidth="1" style="26" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="24">
+    <row r="1" ht="18" customHeight="1" s="26">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>編號</t>
@@ -697,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="130" customHeight="1" s="24">
+    <row r="2" ht="130" customHeight="1" s="26">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>D-01</t>
@@ -768,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="130" customHeight="1" s="24">
+    <row r="3" ht="130" customHeight="1" s="26">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>D-02</t>
@@ -796,7 +796,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -834,13 +834,65 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>尚未修正</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="130" customHeight="1" s="24">
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【討論收斂於 2026-05-08，經 /spectra:discuss】
+設計決策（4 個議題）：
+• Q1 approve 性質：採位元層級（不採流程層級），與 view/edit 不互斥
+• Q2 row-level 形式：採 Named Predicate Registry（不採 SQL 表達式 / UI builder / 純 enum）
+• Q3 既有資料：採激進 fail-safe（既有 200 筆自動 0/NULL/NULL，HR 上線自勾）
+• Q6 整合策略：D-02-core + D-05 同 change，approve 鋪路為未來 L0-Workflow 的前提（不撞牆）
+收斂於決議 9-12：
+• 9 approve middleware 純鋪路，不附示範審核端點
+• 10 org_unit_scope predicate 採遞迴版本，不做 strict 變體
+• 11 既有 5 角色 approve 維持 fail-safe
+• 12 role-management-page row_filter 下拉對所有 features 一致顯示
+Schema 變更：role_feature_perms 加 3 欄（can_approve / approve_scope / row_filter_key）
+Middleware：ROW_FILTERS registry 註冊 4 個首發 predicate（interview_assigned / subordinate_only / self_only / org_unit_scope）+ filterByScope 整合 row_filter + requireApprovePerm middleware
+雙清單同步：tenant-schema.js + tenant-db-manager.js 雙路徑驗證通過
+</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>【實作完成 2026-05-08，OpenSpec change：rbac-row-level-and-interview-scope】
+Schema：
+• role_feature_perms 擴 3 欄（can_approve INTEGER NOT NULL DEFAULT 0、approve_scope CHECK NULL/self/department/company、row_filter_key TEXT NULL）
+• 雙清單同步（tenant-schema.js initTenantSchema 直接含新欄位；tenant-db-manager.js _runMigrations 加 ROLE_FEATURE_PERMS_MIGRATIONS 共用常數，3 條冪等 ALTER TABLE）
+Middleware（permission.js）：
+• ROW_FILTERS registry 註冊 4 個 predicate：interview_assigned / subordinate_only / self_only / org_unit_scope（遞迴版本）
+• mergeFeaturePerms 擴 return 含 can_approve / approve_scope / row_filter_key（多角色合併規則：can_approve OR / approve_scope 取最大 / row_filter_key least-restrictive — bugfix：action_level='none' 不貢獻 row_filter merge）
+• filterByScope 整合 row_filter（短路：scope=1=0 不執行 predicate；predicate=1=0 整體 1=0；row_filter=NULL 向後相容）
+• requireApprovePerm(featureId) middleware（純鋪路，等 L0-Workflow 啟用）
+• applyRowFilter unknown key → '1=0' deny by default
+• 安全：所有 routes 確保 row_filter_key 不來自 client request
+API：
+• GET /api/employee/list 增量擴 ?role=&lt;code&gt; 過濾分支
+• tenant-admin.js PUT /roles/:id/feature-perms 加新欄位驗證 + INSERT 8 欄 + SELECT 8 欄
+• auth.js GET /my-feature-perms 加新欄位（前端 PermissionService 可讀）
+• recruitment.js 4 個 evaluation 端點加 verifyCandidateAccessByRowFilter 單筆存取檢查
+前端：
+• tenant-admin.model.ts 三個 interface 加 3 欄（RoleFeaturePerm / FeaturePermPayload / UserFeaturePerm）
+• role-management-page 加「審核」第三欄（can_approve checkbox + approve_scope 下拉）+「資料列限制」下拉（5 選項：interview_assigned / subordinate_only / self_only / org_unit_scope / NULL）
+• SCSS grid 從 4 欄擴 6 欄（含 RWD）
+測試：
+• test-rbac-merge-multi-role.js（17 assertions）— pure function 多角色合併（含 bugfix scenarios）
+• test-rbac-row-level.js（29 assertions）— ROW_FILTERS registry + buildScopeFilter 整合 + EXPLAIN
+• test-rbac-approve.js（10 assertions）— approve middleware + PUT 驗證
+• test-d05-interviewer-seed.js（28 assertions）— interviewer 系統角色 seed + DELETE 攔截
+• test-d05-interviewer-scope.js（16 assertions）— 三道防線端到端
+驗證：
+• tsc --noEmit + ng build --configuration=development 全綠
+• EXPLAIN QUERY PLAN：interview_assigned EXISTS 子查詢走 idx_invitations_interviewer / idx_interviews_interviewer_at（緩解風險 4）
+• 端到端：HR 排 5/9 面試指派 evan → evan 登入只看到「翔平」一筆候選人
+修改檔案統計：DB 2 / 後端 routes+middleware 6 / 前端 components+services+models+pages 6 / 測試 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="130" customHeight="1" s="26">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>D-03</t>
@@ -938,7 +990,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="130" customHeight="1" s="24">
+    <row r="5" ht="130" customHeight="1" s="26">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>D-04</t>
@@ -1027,7 +1079,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1" s="24">
+    <row r="6" ht="130" customHeight="1" s="26">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>D-05</t>
@@ -1055,7 +1107,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1092,13 +1144,64 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>尚未修正</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="130" customHeight="1" s="24">
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>【討論收斂於 2026-05-08，經 /spectra:discuss】
+設計決策（5 個議題）：
+• Q4 candidate 系統角色：砍除（架構性鎖死已足 — candidates 表獨立於 users + 既有 UUID 機制）
+• Q5 D-05 範圍：限定 RBAC only（評分狀態機 / audit 明列 Non-Goal，分屬未來 change）
+• Q6 指派模式：採 B+（衍生方案，不建 interview_assignments 表 — 反查 interview_invitations + interviews；下拉只列有 interviewer 角色員工）
+實作策略（隨 D-02 同 change）：
+• 系統角色：interviewer 第 6 個系統鎖死角色（不另建 candidate）
+• row_filter：interview_assigned predicate（D-02 ROW_FILTERS registry 之一）
+• 三道防線：UI 下拉 / Feature gate / row filter
+【補充於 2026-05-08，實作中發現並修正 2 個 critical bug】
+• Bug #1：mergeFeaturePerms 把 action_level='none' 的 row 計入 row_filter 解除邏輯
+  — 雙角色用戶（interviewer + employee）的 row_filter 被誤解除 → 看到全部候選人
+  修正：only access-granting rows (action_level != 'none') 參與 row_filter / can_approve / approve_scope merge
+• Bug #2：ROW_FILTERS predicate 用 req.user.userId
+  — 但 interview_invitations.interviewer_id / interviews.interviewer_id / employees.manager_id 都 REFERENCES employees(id) 而非 users(id)
+  修正：改用 req.user.employeeId（authMiddleware 注入），對未綁員工的 user 回 deny（subordinate_only / self_only 同步修正）</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>【實作完成 2026-05-08，隨 D-02 同 OpenSpec change：rbac-row-level-and-interview-scope】
+Schema：
+• 不新增表（衍生方案沿用 interview_invitations + interviews 既有 interviewer_id 欄位 + 既有 idx_invitations_interviewer / idx_interviews_interviewer_at 索引）
+• 不新增 candidate 系統角色（candidates 表獨立於 users 已是架構性鎖死，候選人查狀態走 104 等外部平台）
+新增 interviewer 系統角色：
+• platform.js seedTenantRBAC roles 陣列加第 6 個 { name: 'interviewer', is_system: 1, scope: 'global' }
+• tenant-db-manager.js _runMigrations INSERT OR IGNORE 補入既有租戶
+• DEFAULT_ROLE_FEATURE_PERMS 加 interviewer key：L1.recruitment 為 _e('company','company',{row_filter_key:'interview_assigned'})、L1.decision 與其他 40+ features 全 _n
+• 既有 is_system=1 不可刪除攔截（tenant-admin.js:497）涵蓋 interviewer
+interview_assigned predicate（permission.js）：
+• EXISTS UNION 反查 interview_invitations（status NOT IN 'Cancelled'）+ interviews
+• 用 req.user.employeeId 比對 interviewer_id（兩表都 REFERENCES employees(id)）
+• 支援 candidateTableAlias / candidateIdColumn options（candidates 用 c.id；interview_evaluations 用 ie.candidate_id）
+三道防線：
+• Layer 1：invite-candidate-modal 與 interview.service.ts listActiveEmployees(options) 加 role 選項，呼叫 GET /api/employee/list?role=interviewer 過濾下拉（schedule-interview-modal 為唯讀繼承自 invitation，無下拉需動）
+• Layer 2：requireFeaturePerm('L1.recruitment') 守衛 — 沒 interviewer 角色直接 403
+• Layer 3：buildScopeFilter 自動套 row_filter_key='interview_assigned' EXISTS 過濾 — interviewer 看不到別人候選人
+UI 防呆：modal 加 hint「目前無設定面試官，請至『系統設定 → 員工與帳號管理』為員工加上面試官角色」
+端到端驗證：
+• 5/9 17:30 HR 排面試（candidate=翔平、interviewer=許阿任 employee_id=7b2c9497...）
+• 許阿任登入 → AI智能面試頁面只看到「翔平」一筆（其他候選人完全不可見）
+• admin (super_admin) 登入仍看全部 12 筆（FULL_ACCESS_PERM 不受 row_filter 限制）
+Non-Goals 已實作但拆出：
+• 評分狀態機（draft → submitted → locked）— 屬 interview-evaluation-lifecycle 後續 change
+• interview_evaluations audit log — 歸 D-07 業務稽核日誌
+• 自動接案 / 認領 — 屬未來 ATS 自動化
+• candidate self-service portal — 候選人不登入 Bombus
+測試覆蓋（隨 D-02 同 change，total 100/100 assertions 全綠）：
+• test-d05-interviewer-seed.js（28 assertions）+ test-d05-interviewer-scope.js（16 assertions）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1" s="26">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>D-06</t>
@@ -1171,7 +1274,7 @@
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
     </row>
-    <row r="8" ht="130" customHeight="1" s="24">
+    <row r="8" ht="130" customHeight="1" s="26">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>D-07</t>
@@ -1243,7 +1346,7 @@
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
     </row>
-    <row r="9" ht="130" customHeight="1" s="24">
+    <row r="9" ht="130" customHeight="1" s="26">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>D-08</t>
@@ -1315,7 +1418,7 @@
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
     </row>
-    <row r="10" ht="130" customHeight="1" s="24">
+    <row r="10" ht="130" customHeight="1" s="26">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>D-09</t>
@@ -1387,7 +1490,7 @@
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
     </row>
-    <row r="11" ht="130" customHeight="1" s="24">
+    <row r="11" ht="130" customHeight="1" s="26">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>D-10</t>
@@ -1459,7 +1562,7 @@
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
     </row>
-    <row r="12" ht="130" customHeight="1" s="24">
+    <row r="12" ht="130" customHeight="1" s="26">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>D-11</t>
@@ -1530,7 +1633,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
     </row>
-    <row r="13" ht="130" customHeight="1" s="24">
+    <row r="13" ht="130" customHeight="1" s="26">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>D-12</t>
@@ -1601,7 +1704,7 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
     </row>
-    <row r="14" ht="130" customHeight="1" s="24">
+    <row r="14" ht="130" customHeight="1" s="26">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>D-13</t>
@@ -1673,7 +1776,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
     </row>
-    <row r="15" ht="130" customHeight="1" s="24">
+    <row r="15" ht="130" customHeight="1" s="26">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -1743,7 +1846,7 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
     </row>
-    <row r="16" ht="130" customHeight="1" s="24">
+    <row r="16" ht="130" customHeight="1" s="26">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>D-15</t>
@@ -1815,7 +1918,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
     </row>
-    <row r="17" ht="130" customHeight="1" s="24">
+    <row r="17" ht="130" customHeight="1" s="26">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>D-16</t>
@@ -1963,7 +2066,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="130" customHeight="1" s="24">
+    <row r="18" ht="130" customHeight="1" s="26">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>D-17</t>
@@ -2021,17 +2124,21 @@
 3) 是否要從 D-08 健康監控同時看 Redis 狀態？</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>尚未修正</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>現行已有JWT/Refresh、middleware 強制驗證、防越權編輯等機制</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="n"/>
     </row>
   </sheetData>
@@ -2049,19 +2156,19 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="18" customWidth="1" style="24" min="1" max="1"/>
-    <col width="22" customWidth="1" style="24" min="2" max="2"/>
-    <col width="80" customWidth="1" style="24" min="3" max="3"/>
+    <col width="18" customWidth="1" style="26" min="1" max="1"/>
+    <col width="22" customWidth="1" style="26" min="2" max="2"/>
+    <col width="80" customWidth="1" style="26" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>狀態顏色圖例</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="24">
+    <row r="2" ht="16" customHeight="1" s="26">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2072,13 +2179,13 @@
           <t>已實作</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>需求主體已實作，可能有小幅優化空間</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="24">
+    <row r="3" ht="16" customHeight="1" s="26">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>⚠️</t>
@@ -2089,13 +2196,13 @@
           <t>部分實作</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>已具備基礎能力，部分子能力或邊界情境待補</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="24">
+    <row r="4" ht="16" customHeight="1" s="26">
       <c r="A4" s="15" t="inlineStr">
         <is>
           <t>❌</t>
@@ -2106,79 +2213,79 @@
           <t>未實作</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>現有系統完全缺少對應能力，需從 0 開發</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>修改難易度圖例</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1" s="24">
+    <row r="6" ht="17" customHeight="1" s="26">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>純設定/小幅 UI 調整、無 schema 變動</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="17" customHeight="1" s="24">
+      <c r="C6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="17" customHeight="1" s="26">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>新增 schema 欄位 + API + 1-2 元件，影響範圍可控</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1" s="24">
+      <c r="C7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="17" customHeight="1" s="26">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>跨層大改 / 新模組 / 破壞既有資料模型 / 多遷移同步</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1" s="24">
+      <c r="C8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="26">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>已實作項目（無需修改）</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n"/>
+      <c r="C9" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>編號區間對應模組</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="17" customHeight="1" s="24">
+    <row r="12" ht="17" customHeight="1" s="26">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>D-01 ~ D-05</t>
@@ -2195,7 +2302,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="17" customHeight="1" s="24">
+    <row r="13" ht="17" customHeight="1" s="26">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>D-06 ~ D-09</t>
@@ -2212,7 +2319,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1" s="24">
+    <row r="14" ht="17" customHeight="1" s="26">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>D-10 ~ D-12</t>
@@ -2229,7 +2336,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="17" customHeight="1" s="24">
+    <row r="15" ht="17" customHeight="1" s="26">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>D-13 ~ D-15</t>
@@ -2246,7 +2353,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="17" customHeight="1" s="24">
+    <row r="16" ht="17" customHeight="1" s="26">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>D-16 ~ D-17</t>
@@ -2263,7 +2370,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="17" customHeight="1" s="24">
+    <row r="17" ht="17" customHeight="1" s="26">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>ND-01 ~ ND-02</t>
@@ -2281,95 +2388,95 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>來源檔案資訊</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="24">
+    <row r="20" ht="16" customHeight="1" s="26">
       <c r="A20" s="12" t="inlineStr">
         <is>
           <t>檔案名稱</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>L0_權限與系統設定_需求確認單_1150424.pdf</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1" s="24">
+      <c r="C20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1" s="26">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>檔案類型</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>PDF（Claude Code Read 工具原生解析）</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1" s="24">
+      <c r="C21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1" s="26">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t>頁數</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>4 頁</t>
         </is>
       </c>
-      <c r="C22" s="26" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1" s="24">
+      <c r="C22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" s="26">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>文件性質</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>SaaS 模組需求確認單 (PRD)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1" s="24">
+      <c r="C23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" s="26">
       <c r="A24" s="12" t="inlineStr">
         <is>
           <t>分析日期</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1" s="24">
+      <c r="C24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1" s="26">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>比對範圍</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Bombus 多租戶 SaaS（租戶管理模組為主）</t>
         </is>
       </c>
-      <c r="C25" s="26" t="n"/>
+      <c r="C25" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B7:C7"/>
@@ -2395,15 +2502,15 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="32" customWidth="1" style="24" min="1" max="1"/>
-    <col width="14" customWidth="1" style="24" min="2" max="2"/>
-    <col width="16" customWidth="1" style="24" min="3" max="3"/>
-    <col width="14" customWidth="1" style="24" min="4" max="4"/>
-    <col width="12" customWidth="1" style="24" min="5" max="5"/>
-    <col width="14" customWidth="1" style="24" min="6" max="8"/>
+    <col width="32" customWidth="1" style="26" min="1" max="1"/>
+    <col width="14" customWidth="1" style="26" min="2" max="2"/>
+    <col width="16" customWidth="1" style="26" min="3" max="3"/>
+    <col width="14" customWidth="1" style="26" min="4" max="4"/>
+    <col width="12" customWidth="1" style="26" min="5" max="5"/>
+    <col width="14" customWidth="1" style="26" min="6" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="24">
+    <row r="1" ht="18" customHeight="1" s="26">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>模組</t>
@@ -2445,17 +2552,17 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="24">
+    <row r="2" ht="17" customHeight="1" s="26">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L0-RBAC 多層角色權限</t>
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>0</v>
@@ -2473,7 +2580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1" s="24">
+    <row r="3" ht="17" customHeight="1" s="26">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L0-SSO 共用認證/稽核/監控</t>
@@ -2501,7 +2608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="24">
+    <row r="4" ht="17" customHeight="1" s="26">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L0-Org 集團組織圖</t>
@@ -2529,7 +2636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" s="24">
+    <row r="5" ht="17" customHeight="1" s="26">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L0-Emp 員工資料/代碼</t>
@@ -2557,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1" s="24">
+    <row r="6" ht="17" customHeight="1" s="26">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L0-SaaS 架構/越權</t>
@@ -2585,17 +2692,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1" s="24">
+    <row r="7" ht="17" customHeight="1" s="26">
       <c r="A7" s="21" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="22" t="n">
         <v>3</v>
@@ -2627,15 +2734,15 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="10" customWidth="1" style="24" min="1" max="1"/>
-    <col width="16" customWidth="1" style="24" min="2" max="2"/>
-    <col width="60" customWidth="1" style="24" min="3" max="3"/>
-    <col width="50" customWidth="1" style="24" min="4" max="4"/>
-    <col width="60" customWidth="1" style="24" min="5" max="5"/>
-    <col width="22" customWidth="1" style="24" min="6" max="6"/>
+    <col width="10" customWidth="1" style="26" min="1" max="1"/>
+    <col width="16" customWidth="1" style="26" min="2" max="2"/>
+    <col width="60" customWidth="1" style="26" min="3" max="3"/>
+    <col width="50" customWidth="1" style="26" min="4" max="4"/>
+    <col width="60" customWidth="1" style="26" min="5" max="5"/>
+    <col width="22" customWidth="1" style="26" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="24">
+    <row r="1" ht="18" customHeight="1" s="26">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>編號</t>
@@ -2667,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="110" customHeight="1" s="24">
+    <row r="2" ht="110" customHeight="1" s="26">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ND-01</t>
@@ -2701,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="110" customHeight="1" s="24">
+    <row r="3" ht="110" customHeight="1" s="26">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ND-02</t>

--- a/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
+++ b/bombus-system/docs/客戶回饋比對分析_L0權限與系統設定_20260429.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alifrt/Desktop/Bombus/bombus-system/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D8F86-119E-F142-AD3F-34BBE092E768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFECE77C-56EA-AF42-AD24-C3263EDD5AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
     <sheet name="非功能需求附錄" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">修訂需求總表!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">修訂需求總表!$A$1:$P$18</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="263">
   <si>
     <t>編號</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>—</t>
+  </si>
+  <si>
+    <t>現行已有</t>
   </si>
   <si>
     <t>D-02</t>
@@ -389,6 +392,12 @@
     <t>統一認證 SSO</t>
   </si>
   <si>
+    <t>支援跨模組統一認證登入，整合 OAuth 2.0 與 MFA 多重身份驗證，確保多租戶架構下的資料隔離。</t>
+  </si>
+  <si>
+    <t>在現有 JWT 上加 (1) OAuth 2.0 第三方登入（Google / Microsoft / OIDC）、(2) MFA（TOTP 或簡訊）、(3) 維持租戶資料隔離（OAuth 帳號需綁定租戶）。</t>
+  </si>
+  <si>
     <t>⚠️</t>
   </si>
   <si>
@@ -413,7 +422,10 @@
 3) 是否需要 SAML（企業 SSO） vs OIDC（消費級）？</t>
   </si>
   <si>
-    <t>尚未修正</t>
+    <t>不納入本次調整</t>
+  </si>
+  <si>
+    <t>原規劃不包含OAuth 2.0 與 MFA 多重身份驗證機制，需後續評估實際執行方式與需求</t>
   </si>
   <si>
     <t>D-07</t>
@@ -446,6 +458,9 @@
     <t>1) 留存期限多長？需提供匯出歸檔嗎？
 2) 「複製」操作要記錄到什麼層級？（複製職缺？複製員工資料？）
 3) 自訂追蹤項目的最小粒度 — feature 級夠嗎，還是要到欄位級？</t>
+  </si>
+  <si>
+    <t>尚未修正</t>
   </si>
   <si>
     <t>D-08</t>
@@ -483,6 +498,9 @@
 3) 是否要監控前端錯誤（Sentry-like）— 還是只關心後端？</t>
   </si>
   <si>
+    <t>原wbs預計於115/07/14進行開發並於115/7/28交付，實際完成日期將依定稿日期進行確認，往後推算交付日+14d</t>
+  </si>
+  <si>
     <t>D-09</t>
   </si>
   <si>
@@ -650,6 +668,72 @@
     <t>低</t>
   </si>
   <si>
+    <t>【討論收斂於 2026-05-08，user 拍板三個未決議題 + 後續 user 反饋調整】
+針對「需要討論的問題」三題收斂：
+Q1 預設與最大每頁筆數：
+• 採 default=20、max=200，前端 paginator 選項 [20, 50, 100, 200]
+• 預設值原訂 50，因 demo / 多數小規模租戶（30-100 員工）50 永遠不觸發分頁、看起來像功能壞掉，user 反饋後調整為 20
+• max=200 覆蓋 xlsx 規格「支援 150+ 筆」並預留空間
+Q2 是否需要伺服端排序與多欄位篩選：
+• 必須伺服端排序（客戶端排序在分頁下會失真）
+• 排序欄位走白名單 [name, hire_date, employee_no, department]、order ∈ [asc, desc]，不在白名單回退預設 ORDER BY (department, name)
+• 搜尋對 name / email / employee_no 三欄做 LIKE COLLATE NOCASE（員工編號搜尋是 HR 高頻場景）
+• 既有 dept / status / org_unit_id / role 過濾保留，與分頁/搜尋共存後再 LIMIT
+Q3 匯出全量員工的 API 是否要分離：
+• 採向後相容 opt-in 策略 — 不傳 page 維持 array 回傳（既有 5 個 caller 零修改）；傳 page 才回 { data, total, page, pageSize, totalPages } 物件
+• 匯出 CSV、矩陣視圖、面試/會議下拉、入職文件等繼續用全量陣列，無需分離 endpoint
+範圍：
+• 後端：server/src/routes/employee.js GET /list 擴 page/pageSize/search/sort/order，雙清單同步加 idx_employees_status_org_dept_name 索引（透過 shared EMPLOYEE_MIGRATIONS 常數，單一新增點同步 initTenantSchema 與 _runMigrations 雙路徑）
+• 前端：employee.service.ts 加 getEmployeesPaginated() + EmployeeListResult interface；list 視圖切伺服端分頁（HR /organization/employee-management list 模式 + 員工自助 /employee/profile，兩頁共用同一 endpoint）；矩陣與卡片視圖維持原行為
+• 測試：新建 test-d13-employee-list-pagination.js 涵蓋 6 個 ADDED Requirements
+修改難易度：低（純後端參數擴充 + 前端 paginator + 1 個索引；無新表、無 schema 變更）
+OpenSpec change 名稱：employee-list-pagination
+通過 spectra analyze（Critical/Warning = 0）+ spectra validate</t>
+  </si>
+  <si>
+    <t>【實作完成 2026-05-08，OpenSpec change：employee-list-pagination】
+設計決策（向後相容 opt-in）：
+• Q1 預設/最大筆數：default=50, max=200，前端 paginator 選項 [20,50,100,200]
+• Q2 伺服端排序+搜尋：必須伺服端排序；搜尋對 name/email/employee_no 三欄做 LIKE COLLATE NOCASE
+• Q3 既有 caller 相容：不傳 page 維持 array 回傳，5 個 caller 零修改；傳 page 才回 { data, total, page, pageSize, totalPages }
+Backend 修改：server/src/routes/employee.js GET /list
+• 新 query params：page (1-based) / pageSize (default 50, max 200) / search / sort / order
+• 偵測規則：page !== undefined &amp;&amp; parseInt 非 NaN（防 ?page=undefined / ?page= 誤觸）
+• pageSize bounds：&gt;200 → cap 200；≤0 / 非數值 → 退預設 50
+• 搜尋 prepared statement：name OR email OR employee_no LIKE '%' || ? || '%' COLLATE NOCASE
+• 排序白名單：sort ∈ [name, hire_date, employee_no, department], order ∈ [asc, desc]，不在白名單回退預設 ORDER BY (department, name)
+• N+1 批次合併（managers/users/org_units → positions[]）改套用於 page slice，避免全量 JOIN 後丟棄
+DB Schema：
+• EMPLOYEE_MIGRATIONS（shared constant，雙路徑共用）末尾加 'CREATE INDEX IF NOT EXISTS idx_employees_status_org_dept_name ON employees(status, org_unit_id, department, name)'
+• 此 index 覆蓋預設 ORDER BY 與 status filter 路徑；雙路徑（initTenantSchema 新租戶 + _runMigrations 既有租戶）皆冪等執行
+Frontend：
+• employee.service.ts 新增 getEmployeesPaginated(opts) 方法 + EmployeeListResult interface（data: UnifiedEmployee[]）；既有 getEmployees() / getUnifiedEmployees() 不變
+• employee-management-page list 視圖：
+  - 加 listPage / listPageSize / listSort / listOrder / listResult / listLoading 6 個 signal
+  - toObservable + debounceTime(300) + distinctUntilChanged：當 viewMode='list' 且 search/dept/status/orgUnit/page/pageSize/sort/order 任一變動時，伺服端 fetch
+  - 排序欄頭：name / employee_no / department / hire_date 點擊 toggle asc/desc，page 重置為 1
+  - paginator：每頁筆數下拉 [20,50,100,200]、頁碼 + 顯示「N - M 筆，共 X 筆」
+  - 矩陣視圖（D-03 user-overview-lite）與卡片視圖維持原本 client-side 流程，不受影響
+測試覆蓋（新建 server/src/tests/test-d13-employee-list-pagination.js，49/49 assertions 全綠）：
+• Requirement 1 向後相容：?page=undefined / ?page= / ?page=abc 全退 array fallback
+• Requirement 2 pageSize bounds：default=50 / 200 cap / 0 與負數與字串皆退預設
+• Requirement 3 搜尋：name / employee_no / email 任一命中；不分大小寫；空字串等同無 search
+• Requirement 4 排序：valid sort 順序正確；invalid sort=password / SQL injection 嘗試皆 fallback 不破壞
+• Requirement 5 過濾共存：page + dept / role=interviewer / 三者共存皆正確；total = post-filter 後筆數
+• Requirement 6 索引：透過 idempotent CREATE INDEX IF NOT EXISTS 在 EMPLOYEE_MIGRATIONS 共享常數中保證
+驗證：
+• tsc --noEmit + ng build --configuration=development 全綠
+• demo 租戶 42 員工：?page=1&amp;pageSize=50&amp;sort=hire_date&amp;order=desc 順序正確；?role=interviewer 回 2 人；search='林小美' 命中
+修改檔案統計：DB 1（tenant-schema EMPLOYEE_MIGRATIONS）/ 後端 routes 1（employee.js）/ 前端 services 1 + components 1（component.{ts,html,scss}）/ 測試 1 / xlsx 1
+【補充於 2026-05-08，user 追加範圍】
+employee-list-pagination 同步擴充 `/employee/profile` 員工自助頁：
+• profile-page.component.{ts,html,scss}：同 employee-management-page list 視圖加 6 個 list 信號 + debounceTime(300) toObservable + sortable headers (name/department/hire_date) + paginator [20,50,100,200] 預設 50
+• 複用同一條 GET /api/employee/list?page=N endpoint，無新增後端 API
+• 後端 D-13 整合測試 49/49 仍全綠（無回退）
+• Spec 補 specs/employee-self-service/spec.md MODIFIED 區塊（6 Scenario：view_scope company/department/self + Sortable headers + Debounced search + Page size selector）
+• Proposal 將 profile-page 從 Non-Goals 移出，Modified Capabilities 加 `employee-self-service`</t>
+  </si>
+  <si>
     <t>D-14</t>
   </si>
   <si>
@@ -684,6 +768,9 @@
   </si>
   <si>
     <t>代碼命名規則</t>
+  </si>
+  <si>
+    <t>在模組/功能/資料建立第一筆時，企業可設定專屬的代碼前綴規則；系統將依據該規則，在新增第二筆資料時自動套用並生成流水號。</t>
   </si>
   <si>
     <t>新增 code_naming_rules 表（target_table, prefix, padding, current_seq）；建立第一筆時觸發設定流程；後續資料 INSERT 前自動取下一個流水號。</t>
@@ -827,7 +914,7 @@
     <t>API Middleware 需具有強制驗證機制 (JWT/Refresh Token)，並搭配 Redis 快取確保每次存取不超越租戶與角色邊界。</t>
   </si>
   <si>
-    <t>(1) JWT/Refresh 完整 — 已有；(2) middleware 強制驗證租戶 + 角色 + 作用域邊界 — 已有；(3) Redis 分布式快取 — 目前是內存 LRU，分布式部署需補。</t>
+    <t>(1) JWT/Refresh 完整 — 已有；(2) middleware 強制驗證租戶 + 角色 + 作用域邊界 — 已有；(3) 防越權編輯— 已有。</t>
   </si>
   <si>
     <t>主體已實作，快取技術選型差異。
@@ -1061,39 +1148,150 @@
     <t>D-12 (組織圖同步) ← 主對應</t>
   </si>
   <si>
-    <t>✅</t>
+    <t>角色權限管理擴充：可於同一張角色設定頁針對「模組／功能頁面／資料列」三個層級分別勾選讀、寫、審核權限。
+• 影響範圍：系統設定 → 角色管理頁、所有業務頁面的存取行為。
+• 處理重點：擴充角色權限資料結構（新增審核欄位與資料列限制條件）、後端中介層加入資料列過濾機制、新增四種預設資料列限制（自己 / 部屬 / 面試指派 / 組織子樹）；同步維護新／舊租戶兩條遷移路徑以避免資料不一致。
+• 預計效果：例如設定「部門主管只能查看自己部門員工」、「面試官只能審核被指派候選人」精準權限。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>現行已有</t>
+    <t>員工矩陣視圖右上角新增「匯出 CSV」按鈕：依當前篩選條件匯出員工權限總覽，供企業內控留存。
+• 影響範圍：系統設定 → 員工與帳號管理 → 矩陣視圖。
+• 處理重點：依當前篩選條件即時產製 9 欄員工權限報表（員編 / 姓名 / Email / 部門 / 角色 / 權限範圍 / 帳號狀態 / 匯出時間）、中文化標籤、UTF-8 BOM 編碼以利 Excel 直接開啟。
+• 預計效果：將當前可見員工的權限狀態下載為 CSV 留存，供稽核或內控審查使用。</t>
+  </si>
+  <si>
+    <t>招募流程新增「面試官」系統角色：被指派此角色的員工僅能看到與評分自己被分配的候選人，無法瀏覽他人面試資料。
+• 影響範圍：招募管理 → 面試排程與候選人列表、員工角色設定。
+• 處理重點：新增系統鎖死角色（不可刪除）、建立三道資料隔離防線（前端下拉過濾、後端權限守衛、資料列權限過濾）、相容既有 5 個預設角色；過程中發現並修正兩個關鍵 bug（多角色合併規則、面試資料 ID 對應），確保上線後資料完整。
+• 預計效果：將員工指派為「面試官」即可由系統自動限定其可見範圍，無需手動設定每一筆權限。</t>
+  </si>
+  <si>
+    <t>新增部門時提供三種選項：自行新增 / 從產業範本庫導入（先選產業再選規模）/ CSV 批次匯入。
+• 影響範圍：組織管理 → 公司頁面 → 新增部門入口、平台後台部門範本維護。
+• 處理重點：建立平台層產業類別與部門範本管理（含 8 個共通部門 + 12 產業 × 4-7 個專屬範本）、租戶端三入口統一流程（預檢 → 衝突確認 → 寫入）、CSV 編碼與大小防呆、與 D-15 代碼規則預留銜接點。
+• 預計效果：建立新公司時依產業（科技 / 製造 / 服務等）與規模（微型 / 小型 / 中型 / 大型）一鍵帶入合理的部門結構，再依需要微調。</t>
+  </si>
+  <si>
+    <t>系統操作完整紀錄：將登入、新增、修改、刪除、匯出、複製等業務操作完整留存軌跡，並支援企業自選哪些功能需強制追蹤。
+• 影響範圍：系統設定新增「稽核設定」頁、所有業務頁面的寫入行為。
+• 處理重點：擴充紀錄資料結構以保存「修改前 / 修改後」差異、設計分區與壓縮策略避免影響交易效能、針對自定義追蹤項目提供租戶設定介面。
+• 預先需討論：紀錄保留期（半年 / 1 年 / 永久？）、最小追蹤粒度（功能級或欄位級？）、複製操作的記錄範圍。確認後可估算交付時程。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>原wbs預計於115/07/14進行開發並於115/7/28交付，實際完成日期將依定稿日期進行確認，往後推算交付日+14d</t>
+    <t>員工帳號管理頁新增「員工 × 角色矩陣」第三種視圖：HR 與主管可一次看到全公司所有員工被指派的角色與權限範圍，不需逐筆點員工查詢。
+• 影響範圍：系統設定 → 員工與帳號管理頁。
+• 處理重點：新建矩陣元件（含虛擬捲動以支援 500 員工流暢度）、整合既有篩選條件、複用既有權限編輯彈窗（零修改）、URL 參數同步以利分享連結。
+• 預計效果：以鳥瞰視角檢視全員權限配置、點員工列直接編輯、點角色欄頭反查所有持有者。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>在現有 JWT 上加 (1) OAuth 2.0 第三方登入（Google / Microsoft / OIDC）、(2) MFA（TOTP 或簡訊）、(3) 維持租戶資料隔離（OAuth 帳號需綁定租戶）。</t>
+    <t>組織異動時權限自動同步：當部門或員工調動發生，相關員工權限範圍自動更新，避免人工逐筆清理造成遺漏。
+• 影響範圍：所有涉及部門 / 員工 / 角色變動的功能頁。
+• 處理重點：建立事件監聽機制、設計權限快取失效策略、處理部門刪除時的孤兒權限清理、大型異動（如部門合併）的批次處理避免系統卡頓。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>支援跨模組統一認證登入，整合 OAuth 2.0 與 MFA 多重身份驗證，確保多租戶架構下的資料隔離。</t>
+    <t>部門管理擴充：定義部門間關係（平行協作 / 下游流程）、各部門可設定主軸維度（次部門 / 主管 / 職稱 / 層級）與最終產出價值（Value）。
+• 影響範圍：組織管理 → 部門結構頁、部門編輯彈窗、職能模組與部門連動處。
+• 處理重點：擴充部門資料結構與設定介面、部門協作關係雙向維護、與 D-16 範本庫整合避免資料分裂。
+• 預計效果：清楚標示部門間是平行還是下游關係，例：「業務部下游接到 → 客服部」，並依主軸維度切換查看部門結構。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>原規劃不包含OAuth 2.0 與 MFA 多重身份驗證機制，需後續評估實際執行方式與需求</t>
+    <t>員工跨公司任職管理：員工可同時記錄在多家子公司的職務（含主要任職與兼任）、各任職的部門/職等/職位、起迄日期。
+• 影響範圍：員工管理（個人檔案、列表、詳情頁）、組織圖、跨模組權限計算。
+• 處理重點：新增員工任職資料表、調整員工資料模型對既有頁面影響、跨公司權限規則設計（聯集 / 切換）、既有員工資料遷移補建任職紀錄。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>不納入本次調整</t>
+    <t>員工列表與個人檔案新增「跨公司編號（HQ-xxx）」欄位：自動產生集團統一編號，便於跨子公司辨識同一員工。
+• 影響範圍：員工列表、個人檔案、員工詳情頁。
+• 處理重點：新增編號欄位與唯一性約束、為既有員工資料補建編號、整合 D-15 代碼命名規則的自動產生機制；員工列表點選後可直達個人完整檔案頁。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>已完成</t>
+    <t>代碼自動產生機制：員工編號、部門編號等可由企業自訂前綴規則（例如 HQ-、ENG-、HR- 等），系統建立後續資料時自動延續前綴並產生流水號。
+• 影響範圍：員工新增、部門新增、職缺新增、考核設定等多個業務頁的「代碼」欄位。
+• 處理重點：建立代碼規則設定資料結構、處理流水號並發遞增（避免兩人同時建立資料時編號重複）、提供「導入既有手動代碼」的轉換工具、串接全模組統一介面。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>在模組/功能/資料建立第一筆時，企業可設定專屬的代碼前綴規則；系統將依據該規則，在新增第二筆資料時自動套用並生成流水號。</t>
+    <r>
+      <t xml:space="preserve">員工列表頁面整體升級：新增「分頁瀏覽 + 搜尋 + 欄位排序」功能。
+• 影響範圍：兩處員工列表（系統設定 → 員工與帳號管理、員工檔案頁）。
+• 處理重點：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 調整後端員工查詢邏輯，新增分頁、搜尋、排序的支援；
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 重整兩個列表頁面 UI，確保既有的部門/狀態/權限範圍篩選不受影響；
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>③</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 新增資料庫索引以維持大量員工下的查詢速度；
+• 完成後可以：以姓名／員編／Email 直接搜尋員工、點欄頭依到職日/部門/姓名排序、依需要切換每頁筆數（20/50/100/200），員工人數成長後依然順暢。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>預計提供測試時間</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>預計處理說明</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1101,7 +1299,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1141,6 +1339,27 @@
       <b/>
       <sz val="10"/>
       <name val="Apple Color Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1240,7 +1459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1304,15 +1523,40 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1615,8 +1859,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1627,11 +1871,13 @@
     <col min="8" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="50" customWidth="1"/>
+    <col min="13" max="13" width="63.3984375" style="27" customWidth="1"/>
     <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="28" style="32" customWidth="1"/>
+    <col min="16" max="16" width="129.3984375" style="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" customHeight="1">
+    <row r="1" spans="1:16" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1668,14 +1914,20 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="26" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="130" customHeight="1">
+      <c r="O1" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="P1" s="28" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="130" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1712,669 +1964,769 @@
       <c r="L2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>241</v>
+      <c r="M2" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="130" customHeight="1">
+      <c r="O2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="130" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="M3" s="25" t="s">
+        <v>36</v>
+      </c>
       <c r="N3" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="130" customHeight="1">
+        <v>37</v>
+      </c>
+      <c r="O3" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P3" s="29" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="130" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="130" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="O4" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="130" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="130" customHeight="1">
+        <v>58</v>
+      </c>
+      <c r="O5" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="130" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>240</v>
+        <v>62</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P6" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="130" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="130" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="L7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="130" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" ht="130" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="25"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="31">
+        <v>46164</v>
+      </c>
+      <c r="P8" s="29" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="130" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" ht="130" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="M9" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="130" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="130" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" ht="130" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="M11" s="25"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="31">
+        <v>46164</v>
+      </c>
+      <c r="P11" s="29" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="130" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="25"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="31">
+        <v>46164</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="130" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="31">
+        <v>46164</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="234" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="O14" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="130" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="25"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="130" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="G16" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="130" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="130" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="130" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" ht="130" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="130" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="M16" s="25"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P16" s="29" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="203" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="130" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" ht="130" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>136</v>
-      </c>
       <c r="L17" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>161</v>
+        <v>35</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>170</v>
       </c>
       <c r="N17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="O17" s="31">
+        <v>46157</v>
+      </c>
+      <c r="P17" s="29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="130" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="130" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>240</v>
+        <v>175</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>19</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>24</v>
@@ -2382,13 +2734,19 @@
       <c r="L18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>171</v>
+      <c r="M18" s="25" t="s">
+        <v>180</v>
       </c>
       <c r="N18" s="2"/>
+      <c r="O18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="25" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P18" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2405,221 +2763,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="A1" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="6" spans="1:3" ht="17" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="24"/>
+        <v>142</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="36"/>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="C7" s="24"/>
+        <v>46</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="36"/>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="24"/>
+        <v>34</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="36"/>
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="24"/>
+      <c r="B9" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="36"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+      <c r="A11" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="A19" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
     </row>
     <row r="20" spans="1:3" ht="16" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" s="24"/>
+        <v>208</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="36"/>
     </row>
     <row r="21" spans="1:3" ht="16" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" s="24"/>
+        <v>210</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" s="36"/>
     </row>
     <row r="22" spans="1:3" ht="16" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="24"/>
+        <v>212</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="36"/>
     </row>
     <row r="23" spans="1:3" ht="16" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="24"/>
+        <v>214</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="36"/>
     </row>
     <row r="24" spans="1:3" ht="16" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="C24" s="24"/>
+        <v>216</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="36"/>
     </row>
     <row r="25" spans="1:3" ht="16" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="C25" s="24"/>
+        <v>218</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2632,8 +2990,8 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B7:C7"/>
@@ -2661,30 +3019,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B2" s="11">
         <v>5</v>
@@ -2710,7 +3068,7 @@
     </row>
     <row r="3" spans="1:8" ht="17" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B3" s="17">
         <v>0</v>
@@ -2736,7 +3094,7 @@
     </row>
     <row r="4" spans="1:8" ht="17" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B4" s="17">
         <v>0</v>
@@ -2762,7 +3120,7 @@
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B5" s="17">
         <v>0</v>
@@ -2788,7 +3146,7 @@
     </row>
     <row r="6" spans="1:8" ht="17" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B6" s="17">
         <v>0</v>
@@ -2814,7 +3172,7 @@
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B7" s="22">
         <v>5</v>
@@ -2862,59 +3220,59 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="110" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="110" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
